--- a/data/Indicador_Devolucao_Base.xlsx
+++ b/data/Indicador_Devolucao_Base.xlsx
@@ -2465,7 +2465,7 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2553,7 +2553,7 @@
         <v>33</v>
       </c>
       <c r="C15">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2575,7 +2575,7 @@
         <v>31</v>
       </c>
       <c r="C17">
-        <v>5029</v>
+        <v>5024</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2630,7 +2630,7 @@
         <v>36</v>
       </c>
       <c r="C22">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2729,7 +2729,7 @@
         <v>68</v>
       </c>
       <c r="C31">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6744,7 +6744,7 @@
         <v>32</v>
       </c>
       <c r="C396">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -6755,7 +6755,7 @@
         <v>33</v>
       </c>
       <c r="C397">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -6766,7 +6766,7 @@
         <v>35</v>
       </c>
       <c r="C398">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -6777,7 +6777,7 @@
         <v>31</v>
       </c>
       <c r="C399">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -6810,7 +6810,7 @@
         <v>36</v>
       </c>
       <c r="C402">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -6821,7 +6821,7 @@
         <v>64</v>
       </c>
       <c r="C403">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -6843,7 +6843,7 @@
         <v>44</v>
       </c>
       <c r="C405">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="406" spans="1:3">
